--- a/r5-ELGA-MOPED-256-Beispiele-für-maskierte-Ressourcen-erstellen/ValueSet-moped-AbrechnungsRelevanz-valueset.xlsx
+++ b/r5-ELGA-MOPED-256-Beispiele-für-maskierte-Ressourcen-erstellen/ValueSet-moped-AbrechnungsRelevanz-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T14:27:25+00:00</t>
+    <t>2024-11-11T10:32:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
